--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdrepovaluationtrade/TrdRepoValuationTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdrepovaluationtrade/TrdRepoValuationTrade001.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>交易编号</t>
   </si>
@@ -81,6 +81,10 @@
   </si>
   <si>
     <t>币种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回购类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,25 +466,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.1796875" customWidth="1"/>
     <col min="2" max="2" width="17.6328125" customWidth="1"/>
     <col min="3" max="3" width="18.6328125" customWidth="1"/>
     <col min="4" max="4" width="24.36328125" customWidth="1"/>
-    <col min="5" max="8" width="14.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="4" customWidth="1"/>
-    <col min="10" max="11" width="14.26953125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14.90625" style="8" customWidth="1"/>
-    <col min="13" max="13" width="10.6328125" customWidth="1"/>
-    <col min="14" max="14" width="13.81640625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="14.36328125" customWidth="1"/>
-    <col min="17" max="17" width="12.36328125" customWidth="1"/>
+    <col min="5" max="9" width="14.453125" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="4" customWidth="1"/>
+    <col min="11" max="12" width="14.26953125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="10.6328125" customWidth="1"/>
+    <col min="15" max="15" width="13.81640625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="15.81640625" style="8" customWidth="1"/>
+    <col min="17" max="17" width="14.36328125" customWidth="1"/>
+    <col min="18" max="18" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -499,42 +503,45 @@
       <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="I2" s="5"/>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
